--- a/Input.xlsx
+++ b/Input.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10402"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sayanchatterjee/Nextcloud/Work/BlackCoffer/Data-Extraction-and-NLP/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F195D18-2A56-6B40-9BEC-A2D3E1DCA809}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD03B272-C7FE-484E-865D-69715139DB4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="18360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>URL_ID</t>
   </si>
@@ -33,41 +33,59 @@
     <t>URL</t>
   </si>
   <si>
-    <t>Nasher Miles Bag</t>
+    <t>Nothing Phone 3a</t>
   </si>
   <si>
-    <t>https://www.amazon.in/dp/B0DNQV9LKB?th=1&amp;psc=1</t>
+    <t>https://www.amazon.in/Nothing-Phone-White-256GB-Storage/dp/B0DZNP1MN3/ref=sr_1_2?crid=28KDOARO7T5AB&amp;dib=eyJ2IjoiMSJ9.k4LDU1LEvT_DhwCVqJxo_OU04GRP-iBZbw7WF59DYJmmsDs_-8sGogafJ3PWggWVwm7u0ZZuG5mjfDgwZKVERNOyOyEIu_31NNHQhQAQ-nwRHok4G_WSuoTOBDRnIN0DIPNlfun7WovlP6FcHcU60F15THPi_Ce4gvUycMIMDwKjmacKheVUB1mfFPd9PCV1BWqncjQoN-Z7UEjTXpHHCRjktsYNxG3sKJWsw0d9Pgc.1-uK6re4x09tFzUk6VoIDs9mPizwua3TcAAMzzAey6Q&amp;dib_tag=se&amp;keywords=nothing+phone+3a&amp;qid=1748537458&amp;sprefix=nothi,aps,246&amp;sr=8-2</t>
   </si>
   <si>
-    <t>Ugreen Charger</t>
+    <t>https://www.amazon.in/Samsung-Galaxy-Smartphone-Graphite-Storage/dp/B0DHL7YT5S/ref=sr_1_3?crid=2RBF62FWJ6B00&amp;dib=eyJ2IjoiMSJ9.0BWpZ4ImHW1ZfRnJShi1zt8rS2ZXr8WafZOkgOSNJy6ZEfZ1hwYeKXLo-_RuJx_SP6q3kZ5oHy2xRo6ULiehbeSwws5GCN1AbOWSwhpcPah50e9AED9-5JAS7BMHO8KvX4o_dnRI6mUlkSQwtEdNDqZG81K-wfO7o8zA0-Ox-qKK7OA56W4NHuA6-8FyspcAJjF5yeHBAqIAKEPxDIVNR8aemN5h3BAsdzOTg1zQdXo.qL_kbcmjSDyS6paC8Fc_O02S9a0gPjjgIlZtBHkM4Vs&amp;dib_tag=se&amp;keywords=samsung+s24+fe+5g&amp;qid=1748537484&amp;sprefix=samsun,aps,255&amp;sr=8-3</t>
   </si>
   <si>
-    <t>https://www.amazon.in/UGREEN-Charger-RobotGaN-Compatible-MacBook/dp/B0CQ2F185Z/ref=sr_1_3?dib=eyJ2IjoiMSJ9.2RnPQt4UKN2p23clX4O6I2zTzS5p62k2hmIYYU6eASfcu-uZiPrbnyByFR17lsupJh7EhSt2NDpHwFGFoUkrYet-sDf5ofD0YRlkwyID1TuIhLiSXSQ8NFq4LHM3inDIsZLgTCvt2hV0HZXnqvqi4GpzUZ0PZQK0eisUJIQRHq63dyBgXtSkCWV47-oIQOM2fP8jLUwHZeeR0NMG6sLvtv9NTHFd12g22C4lWSpDS5Q.hkbpkCzx6hagsVsoO9Teb7yqVRlXBc3QXVACKywoL40&amp;dib_tag=se&amp;keywords=ugreen+charger&amp;qid=1744190195&amp;sr=8-3</t>
+    <t>Sony PlayStation®5 Digital Edition (slim) Console Video Game</t>
   </si>
   <si>
-    <t>https://www.amazon.in/iPhone-16e-128-Intelligence-Supersized/dp/B0DXQH1DBS/ref=sr_1_3?crid=3F7MCBXZZNOPD&amp;dib=eyJ2IjoiMSJ9.McnHkXYqSX3ITYdLTWgepcOzOthZPc6RN8ugAgMC6Pmn7jv0FaRUj61A-HBqRwVPiHF2XP52K0rxY98fVTcl3fU7RWMiuQ0Nbc3uzF44IsjOI80xnrEBkvryOOdi7EwgXCnL1p9tPZsaajQCVU3IKutJCm4kwGFmaAGMJxnbqAfHIy7LZg2o0P_uQYTQi6nG3OJF7kQk8l8poX5wrjgVe5QKmgCsenMKiEdPgrJvRe8.6e03b7DaPYdK-bW_P9Qn-vi9xMLxNQMU-DYlwivBOWc&amp;dib_tag=se&amp;keywords=iphone+16e&amp;qid=1744190218&amp;sprefix=iphone+16,aps,327&amp;sr=8-3</t>
+    <t>https://www.amazon.in/Sony-PlayStation%C2%AE5-Digital-Edition-slim/dp/B0CY5QW186/ref=sr_1_1?crid=1HILSOLSM638P&amp;dib=eyJ2IjoiMSJ9.pFhgCqcURNHp7Ghh6tpkbnpMS-EPEWOhlo_-YgjavWwZ-kEtUvaKOw7qV5XV-mB3fg-5LyWnXgR1pItjsmQWM-jj2wKAAOgmKNNNtoiqdn78i5oXxajDcrq3lb1p82ZGo7r5uXLGLUcsFEqBDHv5xbIj7uH3EX37_8xmVYmOd6gLcSYuWITMdsVuU2uCbHv4MOIc5w6fI3DojbgPlEWXPI3O3-qh6u4puUatXYP2RMA.IErUARhzqQ1-kuqIXNL4yTseSUcuSl1pT_PM04CPSwo&amp;dib_tag=se&amp;keywords=PS5&amp;qid=1748537909&amp;sprefix=ps5,aps,275&amp;sr=8-1</t>
   </si>
   <si>
-    <t>Iphone !6e</t>
+    <t>Samsung Galaxy S25 Ultra</t>
   </si>
   <si>
-    <t>https://www.amazon.in/Samsung-Galaxy-Smartphone-Titanium-Storage/dp/B0CS5XW6TN/ref=sr_1_3_mod_primary_new?crid=I66U25A4SGOZ&amp;dib=eyJ2IjoiMSJ9.hv6NA5ualu9lei5y5vIe2MPO39xHMtlvi1ack7oCX2Y1ke_541CeHWU4vyxE_0N4fhv05XPcKPISDYQy3vd1DHG9W-lB61VfKmdRedKrrnAbdEaelupXHddRjTEL_DHCnOxtJdGfoyMv4jCaQ-JMzjKTVYkd7nNOV5IWVSmtQRC71VtvpFmt2MkaIExv2WoETPBdweilDphhPJ5VSMwCTdE_UrN0qR2lc4MKaSJcwB4.jkld_9uvrJaFdH2P99D8DLp8gwi8EY4O0jj875rxP7A&amp;dib_tag=se&amp;keywords=samsung+s24+ultra+5g+mobile&amp;qid=1744197000&amp;sbo=RZvfv//HxDF+O5021pAnSA%3D%3D&amp;sprefix=sa,aps,347&amp;sr=8-3&amp;th=1</t>
+    <t>https://www.amazon.in/Samsung-Smartphone-Titanium-Storage-Included/dp/B0DSKMKJV5/ref=sr_1_3?crid=1LYSSGDKQ9KGQ&amp;dib=eyJ2IjoiMSJ9.6F9zxmqbhCO38LI-LW5u6uX5p_i9BhrpRmOubwMF6wjPDIO6VZkyfmdBNJz4oEp1n-wsQhHaCVuyrZXbVnKaX4XlxHTtW-aVZ9kFV_8e8489N8p048SHSJ19GWFAWIIldOyJ0kFxNaZeFqctwXdSfXP94sJV8txJrNV3EqzCtVZ5aIMSBoGMkkcCfY7qtQSOQxyVVP4Qw4B4jcwbD4mqfo9J4Aeck72a52mXj7sjzNk.v2XhDgp1crT3P9vuf34bKRiz-zb-AbcLZ7xiomulUBg&amp;dib_tag=se&amp;keywords=Samsung+Galaxy+S25+Ultra&amp;qid=1748551919&amp;sprefix=samsung+galaxy+s25+ultra,aps,513&amp;sr=8-3</t>
   </si>
   <si>
-    <t>Samsung Galaxy S24 Ultra 5G</t>
+    <t>vivo X200 Pro</t>
   </si>
   <si>
-    <t>https://www.amazon.in/dp/B0D7VKMLGD/?_encoding=UTF8&amp;pf_rd_p=9acdf892-017e-42b7-bad2-b4d0ddccbc5e&amp;pf_rd_r=1SAXGECSX0RBZTXF9M45</t>
+    <t>https://www.amazon.in/Titanium-Storage-Additional-Exchange-Offers/dp/B07WDJMX16/ref=sr_1_3?crid=1AMENWB5GO0DY&amp;dib=eyJ2IjoiMSJ9.RW_o5BJcY4Y9WG3FGpJDNY2E7rRbskCmv8HFUmg4n6EViv74acd93v3uxtgVfdbhVM6z7SjbBurkA7pSLQTQfuRw1Ay7dLi6_h0jTqdTYgHGcitGIzlJHHAkTu3a1TOIdZWViQj1lW6yvrg-JBZixt-hLMm9vuDYrLg5fheZ6F4EWzLZD1YnYq4k6STINjwq5959_bqJ_EFSE4T5Ugv2vh86OYG2lhh2qjHrOggU0wQ.v_xGoTBUz1SzSFDlDdfK1T8yuNpLOIlYAz6S-CXzweY&amp;dib_tag=se&amp;keywords=vivo+X200+Pro&amp;qid=1748551943&amp;sprefix=vivo+x200+pro,aps,376&amp;sr=8-3</t>
   </si>
   <si>
-    <t>OnePlus Nord 4 5G (Obsidian Midnight, 8GB RAM, 256GB Storage)</t>
+    <t>https://www.amazon.in/Xiaomi-Silver-Chrome-Leica-Quad-Camera/dp/B0DYV4177R/ref=sr_1_3?crid=3BFA6EUJA1KBY&amp;dib=eyJ2IjoiMSJ9.SIwGDtLsGB9zcjOAi-WPna8OoNbV1ZjtaKLSccrPQieStqFpMRS9_hILl-YOrjyfMXIRMOcSLY-HVmOdr2KiKExGLDMLhycRMWdd9sP7EiYC4aFvvYSCLHYE7T1rjAAXrGYdHe2VMIYbRGoYQhEOI4BY90flXzumiCik2orxwlEicoe-vqfG0TQ6XjhUqzw57nCbfg1AqO04Vw3AP6dIO0GJ6_F6kd-NREougY5jYbg.eMEs9lMucx0-o1MQhp-JiQCdGqhUOm9iqfjDohdhhq8&amp;dib_tag=se&amp;keywords=Xiaomi+15+Ultra&amp;qid=1748552015&amp;sprefix=xiaomi+15+ultra,aps,359&amp;sr=8-3</t>
+  </si>
+  <si>
+    <t>Xiaomi 15 Ultra</t>
+  </si>
+  <si>
+    <t>OnePlus 13</t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/OnePlus-13-512GB-Midnight-Ocean/dp/B0DQ8MJYXF/ref=sr_1_3?crid=JVJRW7NMRVIP&amp;dib=eyJ2IjoiMSJ9.ATeYA3KrH9Wb0fbjsbUzvtebcejt3UeUtsz2bSnFdjZYuLZBvPtXKM4JIBLI-ht0IIJ7nHMgy7FCuP-pORHia87pzib1pOvGjv4nb7ZTrqtWuOOJzoukimXDo-l1LC_z6dhpr2BQJEqQz77X7qvpDhekxkm0TO02vMcjqNGLaG23Vzq9-SHIatBT6p63iomGiONoZRyuLO7meIrvwtD2BuKQtDbHVNYz1oy-mCmruqo.uyLDm6GazzMGSo91Vn7lbg0r6sgkbQmiHFaIQl19I84&amp;dib_tag=se&amp;keywords=OnePlus+13&amp;qid=1748552079&amp;sprefix=oneplus+13,aps,457&amp;sr=8-3</t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/Motorola-razr-60-Ultra-Snapdragon%C2%AE/dp/B0F5HVFVKH/ref=sr_1_3?crid=2TMI2QFCK8A8Z&amp;dib=eyJ2IjoiMSJ9.tKCy0Zp_GAMheDynKgHIKQdV9qz4L1fD3DZDQQhhswY8mlPoCpplfNktf4VUGAfGLCxlcOtf_1ZzPnuhWmxKmiRpLE7i6jY1d-DqR0BxBLlvBMfzgRZEirdESJ3UL-mtgttGySVhoXKEppbruoAsAurLddH6JqfCkxounMBnu950XDmY9mShgErmWowuYWbEBe4ylBxByIZceHSy1eFLF4QEEzqJsryemKLK09aXN8E.uk9Yi-AdiOEX1x37cMYYfHi8bLDw3r-OA7cS4Llvon0&amp;dib_tag=se&amp;keywords=Motorola+Razr+60+Ultra&amp;qid=1748552120&amp;sprefix=motorola+razr+60+ultra,aps,529&amp;sr=8-3</t>
+  </si>
+  <si>
+    <t>Motorola Razr 60 Ultra</t>
+  </si>
+  <si>
+    <t>Samsung S24 FE</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -135,6 +153,14 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -177,10 +203,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -192,8 +219,10 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -410,7 +439,7 @@
   <dimension ref="A1:Z932"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="23.6640625" customWidth="1"/>
+    <col min="1" max="1" width="52.1640625" customWidth="1"/>
     <col min="2" max="2" width="122.5" customWidth="1"/>
     <col min="3" max="26" width="8.6640625" customWidth="1"/>
   </cols>
@@ -449,10 +478,10 @@
     </row>
     <row r="2" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
-      <c r="B2" s="5" t="s">
-        <v>3</v>
+      <c r="B2" s="11" t="s">
+        <v>8</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
@@ -481,10 +510,10 @@
     </row>
     <row r="3" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>5</v>
+      <c r="B3" s="11" t="s">
+        <v>10</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
@@ -513,10 +542,10 @@
     </row>
     <row r="4" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
@@ -545,10 +574,10 @@
     </row>
     <row r="5" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
@@ -575,12 +604,12 @@
       <c r="Y5" s="3"/>
       <c r="Z5" s="3"/>
     </row>
-    <row r="6" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" ht="14" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C6" s="3"/>
       <c r="D6" s="3"/>
@@ -608,8 +637,12 @@
       <c r="Z6" s="3"/>
     </row>
     <row r="7" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="4"/>
-      <c r="B7" s="5"/>
+      <c r="A7" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>3</v>
+      </c>
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
@@ -636,8 +669,12 @@
       <c r="Z7" s="3"/>
     </row>
     <row r="8" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="4"/>
-      <c r="B8" s="5"/>
+      <c r="A8" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>4</v>
+      </c>
       <c r="C8" s="3"/>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
@@ -664,8 +701,12 @@
       <c r="Z8" s="3"/>
     </row>
     <row r="9" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="4"/>
-      <c r="B9" s="5"/>
+      <c r="A9" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>6</v>
+      </c>
       <c r="C9" s="3"/>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
@@ -26536,6 +26577,9 @@
       <c r="Z932" s="3"/>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B2" r:id="rId1" display="https://www.amazon.in/Samsung-Smartphone-Titanium-Storage-Included/dp/B0DSKMKJV5/ref=sr_1_3?crid=1LYSSGDKQ9KGQ&amp;dib=eyJ2IjoiMSJ9.6F9zxmqbhCO38LI-LW5u6uX5p_i9BhrpRmOubwMF6wjPDIO6VZkyfmdBNJz4oEp1n-wsQhHaCVuyrZXbVnKaX4XlxHTtW-aVZ9kFV_8e8489N8p048SHSJ19GWFAWIIldOyJ0kFxNaZeFqctwXdSfXP94sJV8txJrNV3EqzCtVZ5aIMSBoGMkkcCfY7qtQSOQxyVVP4Qw4B4jcwbD4mqfo9J4Aeck72a52mXj7sjzNk.v2XhDgp1crT3P9vuf34bKRiz-zb-AbcLZ7xiomulUBg&amp;dib_tag=se&amp;keywords=Samsung+Galaxy+S25+Ultra&amp;qid=1748551919&amp;sprefix=samsung+galaxy+s25+ultra,aps,513&amp;sr=8-3" xr:uid="{371BD03B-B8E1-984F-9492-24888A668D04}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
